--- a/docs/A2_llave_class_uso/propuesta_homologacion.xlsx
+++ b/docs/A2_llave_class_uso/propuesta_homologacion.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="leyenda_propuesta" sheetId="1" state="visible" r:id="rId3"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="116">
   <si>
     <t xml:space="preserve">id_0_propuesta</t>
   </si>
@@ -145,7 +145,7 @@
     <t xml:space="preserve">Incluye suelo desnudo y categoría residual.</t>
   </si>
   <si>
-    <t xml:space="preserve">Otros arbóreos / plantaciones forestales</t>
+    <t xml:space="preserve">Plantaciones forestales</t>
   </si>
   <si>
     <t xml:space="preserve">Resolvería plantaciones, árboles fuera de bosque, regeneración y masas ribereñas.</t>
@@ -340,6 +340,9 @@
     <t xml:space="preserve">Bosque latifoliado y mixto</t>
   </si>
   <si>
+    <t xml:space="preserve"> Bosques latifoliados y mixtos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Provisional hacia la clase forestal amplia 11.</t>
   </si>
   <si>
@@ -385,9 +388,6 @@
     <t xml:space="preserve">Coníferas denso</t>
   </si>
   <si>
-    <t xml:space="preserve">Densidad queda trazada en el código original.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coníferas ralo</t>
   </si>
   <si>
@@ -397,79 +397,25 @@
     <t xml:space="preserve">Interpretativa como formación dominada por pino/coníferas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Separar si interesa distinguir sabanas de pino de bosque de coníferas cerrado.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Manglares</t>
   </si>
   <si>
     <t xml:space="preserve">Manglar alto</t>
   </si>
   <si>
-    <t xml:space="preserve">Estructura alta queda trazada en el código original.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Manglar bajo</t>
   </si>
   <si>
-    <t xml:space="preserve">Estructura baja queda trazada en el código original.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Otros arbóreo en tierras no agrícola</t>
   </si>
   <si>
     <t xml:space="preserve">Masa arbórea ribereña</t>
   </si>
   <si>
-    <t xml:space="preserve">Interpretativa como cobertura arbórea no agrícola dentro de tierras forestales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recomendado crear 15 Otros arbóreos / vegetación arbórea no agrícola.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agregar 15 Otros arbóreos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plantaciones forestales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVISAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No existe clase equivalente en la propuesta actual.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recomendado crear 15 Plantaciones forestales o asignar según especie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agregar 15 Plantaciones forestales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Árboles fuera de bosque y otras áreas naturales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No existe clase equivalente clara en la propuesta actual.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No mezclar automáticamente con bosques naturales; recomendado crear 15 Otros arbóreos.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Regeneración forestal</t>
   </si>
   <si>
-    <t xml:space="preserve">Interpretativa como cobertura forestal en recuperación.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Si se monitorea restauración/sucesión, conviene mantener clase propia.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bosque de Palmas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpretativa como bosque arbóreo no conífero, no mangle y no seco.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puede requerir clase específica si es relevante localmente.</t>
   </si>
   <si>
     <t xml:space="preserve">Otras</t>
@@ -488,11 +434,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -525,12 +472,18 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -546,7 +499,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFA6"/>
-        <bgColor rgb="FFFFFFD7"/>
+        <bgColor rgb="FFE8F2A1"/>
       </patternFill>
     </fill>
     <fill>
@@ -570,13 +523,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD4EA6B"/>
+        <bgColor rgb="FFE8F2A1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F2A1"/>
         <bgColor rgb="FFFFFFA6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFE8F2A1"/>
       </patternFill>
     </fill>
   </fills>
@@ -625,16 +584,32 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -642,27 +617,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -688,7 +675,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFA6"/>
+          <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -704,14 +691,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -756,6 +735,14 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F2A1"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -793,12 +780,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFD4EA6B"/>
+      <rgbColor rgb="FFE8F2A1"/>
       <rgbColor rgb="FFFFFFA6"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFD4EA6B"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -821,7 +808,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HomologacionLookup" displayName="HomologacionLookup" ref="A1:M41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HomologacionLookup" displayName="HomologacionLookup" ref="A1:M40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="1" name="id_0_doc"/>
     <tableColumn id="2" name="nivel_0_doc"/>
@@ -984,211 +971,213 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:XFD12"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="68.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="68.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="A6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="A7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="A8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="0" t="n">
+      <c r="A9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="A10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="3" t="n">
+    <row r="12" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="XFC12" s="6"/>
+      <c r="XFD12" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1210,1550 +1199,1465 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="59.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="62.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="73.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="38.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="45.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="59.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="38.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="62.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="73.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="38.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="I1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+    <row r="2" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="9" t="n">
         <v>110</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="5" t="n">
+      <c r="G2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+    <row r="3" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="9" t="n">
         <v>111</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="5" t="n">
+      <c r="G3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+    <row r="4" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="9" t="n">
         <v>112</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="5" t="n">
+      <c r="G4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+    <row r="5" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="5" t="n">
+      <c r="G5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+    <row r="6" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="9" t="n">
         <v>122</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="5" t="n">
+      <c r="G6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+    <row r="7" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="9" t="n">
         <v>210</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="5" t="n">
+      <c r="G7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+    <row r="8" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="9" t="n">
         <v>211</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="5" t="n">
+      <c r="G8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+    <row r="9" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="9" t="n">
         <v>212</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="5" t="n">
+      <c r="G9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+    <row r="10" s="10" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="10" t="n">
         <v>220</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="6" t="n">
+      <c r="G10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+    <row r="11" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="9" t="n">
         <v>311</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="5" t="n">
+      <c r="G11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+    <row r="12" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="9" t="n">
         <v>312</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="5" t="n">
+      <c r="G12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+    <row r="13" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="9" t="n">
         <v>313</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="5" t="n">
+      <c r="G13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+    <row r="14" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="9" t="n">
         <v>314</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="5" t="n">
+      <c r="G14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
+    <row r="15" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="9" t="n">
         <v>315</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="5" t="n">
+      <c r="G15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
+    <row r="16" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="9" t="n">
         <v>321</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="5" t="n">
+      <c r="G16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
+    <row r="17" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="9" t="n">
         <v>322</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="5" t="n">
+      <c r="G17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
+    <row r="18" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="9" t="n">
         <v>323</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" s="5" t="n">
+      <c r="G18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
+    <row r="19" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="9" t="n">
         <v>324</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="5" t="n">
+      <c r="G19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
+    <row r="20" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="9" t="n">
         <v>325</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I20" s="5" t="n">
+      <c r="G20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L20" s="5" t="s">
+      <c r="L20" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="n">
+    <row r="21" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="9" t="n">
         <v>331</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="5" t="n">
+      <c r="G21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="22" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
+    <row r="22" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="9" t="n">
         <v>332</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="G22" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="5" t="n">
+      <c r="G22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="L22" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+    <row r="23" s="11" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="11" t="n">
         <v>333</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G23" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I23" s="7" t="n">
+      <c r="G23" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="K23" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="L23" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
+    <row r="24" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I24" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="K24" s="8" t="s">
+      <c r="I24" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J24" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="K24" s="12" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="25" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="n">
+      <c r="L24" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="12" t="n">
         <v>411</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" s="8" t="n">
+      <c r="F25" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I25" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="K25" s="8" t="s">
+      <c r="I25" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>412</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>413</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>414</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>420</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>421</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>422</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>423</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>430</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>431</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>441</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>442</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+    </row>
+    <row r="38" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>444</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>445</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" s="16" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="L25" s="8" t="s">
+      <c r="B40" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="16" t="n">
         <v>91</v>
       </c>
-    </row>
-    <row r="26" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>412</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>413</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>414</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I28" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>420</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>421</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>422</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>423</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="33" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>430</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>431</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="35" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>432</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>441</v>
-      </c>
-      <c r="F36" s="8" t="s">
+      <c r="D40" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="G36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="K36" s="8" t="s">
+      <c r="E40" s="16" t="n">
+        <v>910</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J40" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="L36" s="8" t="s">
+      <c r="L40" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="M36" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="37" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>442</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>443</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>444</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>445</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>910</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>133</v>
-      </c>
-    </row>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/A2_llave_class_uso/propuesta_homologacion.xlsx
+++ b/docs/A2_llave_class_uso/propuesta_homologacion.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jesus\Work\CR\Github\PGBM_actividad_1_diagnostico\docs\A2_llave_class_uso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E681CCD-429D-448D-97F7-5A307D855C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADECE595-AD79-4E2D-A0B3-B048A7A64C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="leyenda_propuesta" sheetId="1" r:id="rId1"/>
-    <sheet name="homologacion" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Propuesta_leyenda" sheetId="3" r:id="rId1"/>
+    <sheet name="leyenda_propuesta" sheetId="1" r:id="rId2"/>
+    <sheet name="homologacion" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -554,7 +554,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -570,7 +570,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -824,6 +823,1311 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADE2C7B-7B86-4289-92D6-0F937B4FDABD}">
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="4" max="4" width="45.44140625" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
+    <col min="6" max="6" width="59" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="38.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>40</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="12">
+        <v>41</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="12">
+        <v>410</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="12">
+        <v>1</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="12">
+        <v>11</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>40</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="12">
+        <v>41</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="12">
+        <v>411</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="12">
+        <v>1</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="12">
+        <v>11</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>40</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="12">
+        <v>41</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="12">
+        <v>412</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="12">
+        <v>1</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="12">
+        <v>11</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>40</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="12">
+        <v>41</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="12">
+        <v>413</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="12">
+        <v>1</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="12">
+        <v>11</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>40</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="8">
+        <v>44</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="8">
+        <v>441</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="8">
+        <v>11</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>40</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="8">
+        <v>44</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="8">
+        <v>444</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="8">
+        <v>11</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>40</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="8">
+        <v>44</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="8">
+        <v>445</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="8">
+        <v>11</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>40</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="8">
+        <v>42</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="8">
+        <v>420</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="8">
+        <v>12</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>40</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="8">
+        <v>42</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="8">
+        <v>421</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="8">
+        <v>12</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>40</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="8">
+        <v>42</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="8">
+        <v>422</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="8">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" s="8">
+        <v>12</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>40</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="8">
+        <v>42</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="8">
+        <v>423</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="8">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="8">
+        <v>12</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>40</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="8">
+        <v>43</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="8">
+        <v>430</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" s="8">
+        <v>13</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>40</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="8">
+        <v>43</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="8">
+        <v>431</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="8">
+        <v>13</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>40</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="8">
+        <v>43</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="8">
+        <v>432</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="8">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="8">
+        <v>13</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>40</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="13">
+        <v>41</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="13">
+        <v>414</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="13">
+        <v>1</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="13">
+        <v>14</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="8">
+        <v>44</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="8">
+        <v>442</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="8">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="8">
+        <v>15</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>30</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="11">
+        <v>31</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="11">
+        <v>311</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="11">
+        <v>2</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="11">
+        <v>21</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>30</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="5">
+        <v>32</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="5">
+        <v>321</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="5">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="5">
+        <v>21</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>30</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="5">
+        <v>32</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="5">
+        <v>322</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="5">
+        <v>2</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="5">
+        <v>21</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>30</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="5">
+        <v>32</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="5">
+        <v>323</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="5">
+        <v>2</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="5">
+        <v>21</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>30</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="5">
+        <v>32</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="5">
+        <v>324</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="5">
+        <v>2</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="5">
+        <v>21</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>30</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="7">
+        <v>32</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="7">
+        <v>325</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="7">
+        <v>2</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="7">
+        <v>21</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>30</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="11">
+        <v>31</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="11">
+        <v>312</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="11">
+        <v>2</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="11">
+        <v>22</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>30</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="11">
+        <v>31</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="11">
+        <v>313</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="11">
+        <v>2</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="11">
+        <v>22</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>30</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="11">
+        <v>31</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" s="11">
+        <v>314</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="11">
+        <v>2</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="11">
+        <v>22</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>30</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="11">
+        <v>31</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="11">
+        <v>315</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="11">
+        <v>2</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="11">
+        <v>22</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>30</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="5">
+        <v>33</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="5">
+        <v>331</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="5">
+        <v>22</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>30</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="5">
+        <v>33</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="5">
+        <v>332</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" s="5">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="5">
+        <v>22</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>30</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="5">
+        <v>33</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="5">
+        <v>333</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="5">
+        <v>2</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="5">
+        <v>22</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>10</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="5">
+        <v>11</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="5">
+        <v>110</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="5">
+        <v>23</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>10</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="5">
+        <v>11</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="5">
+        <v>111</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="5">
+        <v>2</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="5">
+        <v>23</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>10</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="5">
+        <v>11</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="5">
+        <v>112</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G33" s="5">
+        <v>2</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="5">
+        <v>23</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>10</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="11">
+        <v>12</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="11">
+        <v>121</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="11">
+        <v>2</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="11">
+        <v>23</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>20</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="5">
+        <v>21</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="5">
+        <v>210</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" s="5">
+        <v>2</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="5">
+        <v>24</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>20</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="5">
+        <v>21</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="5">
+        <v>211</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="5">
+        <v>24</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>20</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="5">
+        <v>21</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="5">
+        <v>212</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="5">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="5">
+        <v>24</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>10</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="11">
+        <v>12</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="11">
+        <v>122</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G38" s="11">
+        <v>2</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" s="11">
+        <v>25</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>20</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="6">
+        <v>22</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="6">
+        <v>220</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="6">
+        <v>2</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" s="6">
+        <v>25</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="10">
+        <v>90</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="10">
+        <v>91</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E40" s="10">
+        <v>910</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G40" s="10">
+        <v>2</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="10">
+        <v>25</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J42">
+    <sortCondition ref="I1:I42"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -832,7 +2136,7 @@
     <col min="2" max="2" width="31.77734375" customWidth="1"/>
     <col min="3" max="3" width="15.88671875" customWidth="1"/>
     <col min="4" max="4" width="38.5546875" customWidth="1"/>
-    <col min="5" max="5" width="68.109375" customWidth="1"/>
+    <col min="5" max="5" width="84" bestFit="1" customWidth="1"/>
     <col min="16383" max="16384" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1041,7 +2345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="9.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -2509,1309 +3813,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADE2C7B-7B86-4289-92D6-0F937B4FDABD}">
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
-    <col min="4" max="4" width="45.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" customWidth="1"/>
-    <col min="6" max="6" width="59" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="31.77734375" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="10" width="38.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <v>40</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="13">
-        <v>41</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="13">
-        <v>410</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="13">
-        <v>1</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="13">
-        <v>11</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>40</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="13">
-        <v>41</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="13">
-        <v>411</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="13">
-        <v>1</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="13">
-        <v>11</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>40</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="13">
-        <v>41</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="13">
-        <v>412</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="13">
-        <v>1</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="13">
-        <v>11</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>40</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="13">
-        <v>41</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="13">
-        <v>413</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" s="13">
-        <v>1</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="13">
-        <v>11</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>40</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="8">
-        <v>44</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="8">
-        <v>441</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="8">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" s="8">
-        <v>11</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>40</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="8">
-        <v>44</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="8">
-        <v>444</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="8">
-        <v>11</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <v>40</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="8">
-        <v>44</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="8">
-        <v>445</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="8">
-        <v>11</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <v>40</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="8">
-        <v>42</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="8">
-        <v>420</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="8">
-        <v>12</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <v>40</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="8">
-        <v>42</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="8">
-        <v>421</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="8">
-        <v>12</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <v>40</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="8">
-        <v>42</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="8">
-        <v>422</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G11" s="8">
-        <v>1</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I11" s="8">
-        <v>12</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
-        <v>40</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="8">
-        <v>42</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="8">
-        <v>423</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="8">
-        <v>1</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" s="8">
-        <v>12</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <v>40</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="8">
-        <v>43</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="8">
-        <v>430</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="G13" s="8">
-        <v>1</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I13" s="8">
-        <v>13</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
-        <v>40</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="8">
-        <v>43</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="8">
-        <v>431</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" s="8">
-        <v>1</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="8">
-        <v>13</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <v>40</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="8">
-        <v>43</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="8">
-        <v>432</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="8">
-        <v>1</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" s="8">
-        <v>13</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <v>40</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="14">
-        <v>41</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="14">
-        <v>414</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" s="14">
-        <v>14</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
-        <v>40</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="8">
-        <v>44</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="8">
-        <v>442</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="8">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="8">
-        <v>15</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
-        <v>30</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="12">
-        <v>31</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="12">
-        <v>311</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="12">
-        <v>2</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" s="12">
-        <v>21</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>30</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="5">
-        <v>32</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="5">
-        <v>321</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="5">
-        <v>2</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="5">
-        <v>21</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>30</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="5">
-        <v>32</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="5">
-        <v>322</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="5">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I20" s="5">
-        <v>21</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
-        <v>30</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="5">
-        <v>32</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="5">
-        <v>323</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="5">
-        <v>2</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="5">
-        <v>21</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>30</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="5">
-        <v>32</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="5">
-        <v>324</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" s="5">
-        <v>2</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="5">
-        <v>21</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>30</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="7">
-        <v>32</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="7">
-        <v>325</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="7">
-        <v>2</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I23" s="7">
-        <v>21</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>30</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="12">
-        <v>31</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="12">
-        <v>312</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="12">
-        <v>2</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I24" s="12">
-        <v>22</v>
-      </c>
-      <c r="J24" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
-        <v>30</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="12">
-        <v>31</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="12">
-        <v>313</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="12">
-        <v>2</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="12">
-        <v>22</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>30</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="12">
-        <v>31</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="12">
-        <v>314</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" s="12">
-        <v>2</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" s="12">
-        <v>22</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>30</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="12">
-        <v>31</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="12">
-        <v>315</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="12">
-        <v>2</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" s="12">
-        <v>22</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
-        <v>30</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="5">
-        <v>33</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="5">
-        <v>331</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" s="5">
-        <v>2</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" s="5">
-        <v>22</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
-        <v>30</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="5">
-        <v>33</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="5">
-        <v>332</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="5">
-        <v>2</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" s="5">
-        <v>22</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>30</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="11">
-        <v>33</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="11">
-        <v>333</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="11">
-        <v>2</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" s="11">
-        <v>22</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
-        <v>10</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="5">
-        <v>11</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="5">
-        <v>110</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G31" s="5">
-        <v>2</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" s="5">
-        <v>23</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
-        <v>10</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="5">
-        <v>11</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="5">
-        <v>111</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G32" s="5">
-        <v>2</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="5">
-        <v>23</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
-        <v>10</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="5">
-        <v>11</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="5">
-        <v>112</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G33" s="5">
-        <v>2</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I33" s="5">
-        <v>23</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
-        <v>10</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="12">
-        <v>12</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="12">
-        <v>121</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="12">
-        <v>2</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="12">
-        <v>23</v>
-      </c>
-      <c r="J34" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
-        <v>20</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="5">
-        <v>21</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="5">
-        <v>210</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G35" s="5">
-        <v>2</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" s="5">
-        <v>24</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
-        <v>20</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="5">
-        <v>21</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="5">
-        <v>211</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G36" s="5">
-        <v>2</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" s="5">
-        <v>24</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
-        <v>20</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="5">
-        <v>21</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="5">
-        <v>212</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G37" s="5">
-        <v>2</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I37" s="5">
-        <v>24</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
-        <v>10</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="12">
-        <v>12</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="12">
-        <v>122</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G38" s="12">
-        <v>2</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" s="12">
-        <v>25</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
-        <v>20</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="6">
-        <v>22</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="6">
-        <v>220</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="6">
-        <v>2</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" s="6">
-        <v>25</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="10">
-        <v>90</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C40" s="10">
-        <v>91</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E40" s="10">
-        <v>910</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="G40" s="10">
-        <v>2</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I40" s="10">
-        <v>25</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J42">
-    <sortCondition ref="I1:I42"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>